--- a/docs/Lab01/Lab01_ReviewReport_final.xlsx
+++ b/docs/Lab01/Lab01_ReviewReport_final.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tania\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maria-Melania\OneDrive\Documents\Proiect VVSS\VVSS-MyDrinkShop\docs\Lab01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05E678C9-ABA1-4F5D-BAE9-B77A248B91E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="650" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="10296" tabRatio="650"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements Phase Defects" sheetId="7" r:id="rId1"/>
@@ -18,7 +17,7 @@
     <sheet name="Coding Phase Defects" sheetId="5" r:id="rId3"/>
     <sheet name="Tool-basedCodeAnalysis" sheetId="8" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="135">
   <si>
     <t>Document  Title:</t>
   </si>
@@ -423,12 +422,30 @@
   </si>
   <si>
     <t>In metoda `findOne` este posibil sa faca null dereference. Codul returneaza in mod normal un product, dar nu verifica daca exista sau nu, deci daca chiar o returnat un produs sau un null. iar cand incearca sa ia product.getPret() pe acel produs, daca ii null arunca un NullPointerException si nu o sa mai fie in regula order-ul</t>
+  </si>
+  <si>
+    <t>MyDrinkShop_2.0/Linia 40</t>
+  </si>
+  <si>
+    <t>MyDrinkShop_2.0/Linia 46</t>
+  </si>
+  <si>
+    <t>MyDrinkShop_2.0/Linia 63</t>
+  </si>
+  <si>
+    <t>MyDrinkShop_2.0/Linia 71</t>
+  </si>
+  <si>
+    <t>MyDrinkShop_2.0/Linia 83</t>
+  </si>
+  <si>
+    <t>MyDrinkShop_2.0/Linia 97</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -825,53 +842,53 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="16" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="16" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -891,9 +908,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -931,9 +948,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -968,7 +985,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1003,7 +1020,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1176,25 +1193,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:J27"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.90625" style="6"/>
-    <col min="2" max="2" width="12.1796875" style="6" customWidth="1"/>
-    <col min="3" max="3" width="16.1796875" style="6" customWidth="1"/>
-    <col min="4" max="4" width="22.54296875" style="6" customWidth="1"/>
-    <col min="5" max="5" width="41.453125" style="6" customWidth="1"/>
-    <col min="6" max="8" width="8.90625" style="6"/>
+    <col min="1" max="1" width="8.88671875" style="6"/>
+    <col min="2" max="2" width="12.21875" style="6" customWidth="1"/>
+    <col min="3" max="3" width="16.21875" style="6" customWidth="1"/>
+    <col min="4" max="4" width="22.5546875" style="6" customWidth="1"/>
+    <col min="5" max="5" width="41.44140625" style="6" customWidth="1"/>
+    <col min="6" max="8" width="8.88671875" style="6"/>
     <col min="9" max="9" width="21" style="6" customWidth="1"/>
-    <col min="10" max="10" width="14.453125" style="6" customWidth="1"/>
-    <col min="11" max="16384" width="8.90625" style="6"/>
+    <col min="10" max="10" width="14.44140625" style="6" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
@@ -1205,13 +1222,13 @@
       <c r="I1" s="55"/>
       <c r="J1" s="55"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B2" s="61" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B2" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
       <c r="H2" s="3"/>
       <c r="I2" s="17" t="s">
         <v>30</v>
@@ -1220,7 +1237,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H3" s="16" t="s">
         <v>20</v>
       </c>
@@ -1231,14 +1248,14 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C4" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="62" t="s">
+      <c r="D4" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="62"/>
+      <c r="E4" s="57"/>
       <c r="H4" s="16" t="s">
         <v>21</v>
       </c>
@@ -1249,14 +1266,14 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="63" t="s">
+      <c r="D5" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="64"/>
+      <c r="E5" s="59"/>
       <c r="H5" s="16" t="s">
         <v>22</v>
       </c>
@@ -1267,26 +1284,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="54" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="60"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="E6" s="54"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="60" t="s">
+      <c r="D7" s="54" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="60"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="E7" s="54"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="10" t="s">
         <v>4</v>
       </c>
@@ -1300,7 +1317,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B10" s="3">
         <v>1</v>
       </c>
@@ -1314,7 +1331,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B11" s="3">
         <f>B10+1</f>
         <v>2</v>
@@ -1329,7 +1346,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B12" s="3">
         <f t="shared" ref="B12:B25" si="0">B11+1</f>
         <v>3</v>
@@ -1344,7 +1361,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1359,7 +1376,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1374,7 +1391,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1389,7 +1406,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1404,7 +1421,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="17" spans="2:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1419,7 +1436,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1428,7 +1445,7 @@
       <c r="D18" s="3"/>
       <c r="E18" s="15"/>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1437,7 +1454,7 @@
       <c r="D19" s="3"/>
       <c r="E19" s="21"/>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1446,7 +1463,7 @@
       <c r="D20" s="3"/>
       <c r="E20" s="15"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1455,7 +1472,7 @@
       <c r="D21" s="3"/>
       <c r="E21" s="21"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1464,7 +1481,7 @@
       <c r="D22" s="3"/>
       <c r="E22" s="21"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1473,7 +1490,7 @@
       <c r="D23" s="3"/>
       <c r="E23" s="21"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1482,7 +1499,7 @@
       <c r="D24" s="3"/>
       <c r="E24" s="21"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1491,7 +1508,7 @@
       <c r="D25" s="3"/>
       <c r="E25" s="21"/>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C27" s="11" t="s">
         <v>8</v>
       </c>
@@ -1515,23 +1532,23 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:J28"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.90625" style="6"/>
-    <col min="2" max="2" width="12.1796875" style="6" customWidth="1"/>
-    <col min="3" max="4" width="16.1796875" style="6" customWidth="1"/>
-    <col min="5" max="5" width="41.453125" style="6" customWidth="1"/>
-    <col min="6" max="8" width="8.90625" style="6"/>
-    <col min="9" max="9" width="22.08984375" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="8.90625" style="6"/>
+    <col min="1" max="1" width="8.88671875" style="6"/>
+    <col min="2" max="2" width="12.21875" style="6" customWidth="1"/>
+    <col min="3" max="4" width="16.21875" style="6" customWidth="1"/>
+    <col min="5" max="5" width="41.44140625" style="6" customWidth="1"/>
+    <col min="6" max="8" width="8.88671875" style="6"/>
+    <col min="9" max="9" width="22.109375" style="6" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
@@ -1542,13 +1559,13 @@
       <c r="I1" s="55"/>
       <c r="J1" s="55"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B2" s="61" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B2" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
       <c r="H2" s="3"/>
       <c r="I2" s="17" t="s">
         <v>30</v>
@@ -1557,7 +1574,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H3" s="16" t="s">
         <v>20</v>
       </c>
@@ -1568,14 +1585,14 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="65" t="s">
+      <c r="D4" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="65"/>
+      <c r="E4" s="60"/>
       <c r="H4" s="16" t="s">
         <v>21</v>
       </c>
@@ -1586,14 +1603,14 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="66" t="s">
+      <c r="D5" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="67"/>
+      <c r="E5" s="62"/>
       <c r="H5" s="16" t="s">
         <v>22</v>
       </c>
@@ -1604,26 +1621,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="54" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="60"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="E6" s="54"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="60" t="s">
+      <c r="D7" s="54" t="s">
         <v>46</v>
       </c>
-      <c r="E7" s="60"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="E7" s="54"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="10" t="s">
         <v>4</v>
       </c>
@@ -1637,19 +1654,21 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B10" s="3">
         <v>1</v>
       </c>
       <c r="C10" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="28"/>
+      <c r="D10" s="28" t="s">
+        <v>129</v>
+      </c>
       <c r="E10" s="28" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B11" s="3">
         <f>B10+1</f>
         <v>2</v>
@@ -1657,12 +1676,14 @@
       <c r="C11" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="28"/>
+      <c r="D11" s="28" t="s">
+        <v>131</v>
+      </c>
       <c r="E11" s="28" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B12" s="3">
         <f t="shared" ref="B12:B26" si="0">B11+1</f>
         <v>3</v>
@@ -1670,12 +1691,14 @@
       <c r="C12" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="23"/>
+      <c r="D12" s="23" t="s">
+        <v>130</v>
+      </c>
       <c r="E12" s="28" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1688,7 +1711,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1696,12 +1719,14 @@
       <c r="C14" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="D14" s="23"/>
+      <c r="D14" s="23" t="s">
+        <v>132</v>
+      </c>
       <c r="E14" s="28" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1709,12 +1734,14 @@
       <c r="C15" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="D15" s="28"/>
+      <c r="D15" s="28" t="s">
+        <v>133</v>
+      </c>
       <c r="E15" s="28" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1722,12 +1749,14 @@
       <c r="C16" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="23"/>
+      <c r="D16" s="23" t="s">
+        <v>134</v>
+      </c>
       <c r="E16" s="28" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1736,7 +1765,7 @@
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1745,7 +1774,7 @@
       <c r="D18" s="1"/>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1754,7 +1783,7 @@
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1763,7 +1792,7 @@
       <c r="D20" s="1"/>
       <c r="E20" s="2"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1772,7 +1801,7 @@
       <c r="D21" s="1"/>
       <c r="E21" s="2"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1781,7 +1810,7 @@
       <c r="D22" s="1"/>
       <c r="E22" s="2"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1790,7 +1819,7 @@
       <c r="D23" s="1"/>
       <c r="E23" s="2"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1799,7 +1828,7 @@
       <c r="D24" s="1"/>
       <c r="E24" s="2"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1808,7 +1837,7 @@
       <c r="D25" s="1"/>
       <c r="E25" s="2"/>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26" s="3">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -1817,7 +1846,7 @@
       <c r="D26" s="1"/>
       <c r="E26" s="2"/>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C28" s="11" t="s">
         <v>8</v>
       </c>
@@ -1841,24 +1870,24 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="3" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:J34"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.90625" style="6"/>
-    <col min="2" max="2" width="12.1796875" style="6" customWidth="1"/>
-    <col min="3" max="3" width="16.1796875" style="6" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" style="6"/>
+    <col min="2" max="2" width="12.21875" style="6" customWidth="1"/>
+    <col min="3" max="3" width="16.21875" style="6" customWidth="1"/>
     <col min="4" max="4" width="18" style="6" customWidth="1"/>
-    <col min="5" max="5" width="41.453125" style="6" customWidth="1"/>
-    <col min="6" max="8" width="8.90625" style="6"/>
-    <col min="9" max="9" width="26.81640625" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="8.90625" style="6"/>
+    <col min="5" max="5" width="41.44140625" style="6" customWidth="1"/>
+    <col min="6" max="8" width="8.88671875" style="6"/>
+    <col min="9" max="9" width="26.77734375" style="6" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="4"/>
       <c r="B1" s="30" t="s">
         <v>3</v>
@@ -1868,19 +1897,19 @@
       <c r="E1" s="31"/>
       <c r="F1" s="31"/>
       <c r="G1" s="31"/>
-      <c r="H1" s="68" t="s">
+      <c r="H1" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B2" s="56" t="s">
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B2" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
       <c r="F2" s="31"/>
       <c r="G2" s="31"/>
       <c r="H2" s="32"/>
@@ -1891,7 +1920,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B3" s="31"/>
       <c r="C3" s="31"/>
       <c r="D3" s="31"/>
@@ -1908,15 +1937,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B4" s="31"/>
       <c r="C4" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="57" t="s">
+      <c r="D4" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="57"/>
+      <c r="E4" s="66"/>
       <c r="F4" s="31"/>
       <c r="G4" s="31"/>
       <c r="H4" s="32" t="s">
@@ -1929,15 +1958,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B5" s="31"/>
       <c r="C5" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="69" t="s">
+      <c r="D5" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="69"/>
+      <c r="E5" s="68"/>
       <c r="F5" s="31"/>
       <c r="G5" s="31"/>
       <c r="H5" s="32" t="s">
@@ -1950,37 +1979,37 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" s="34"/>
       <c r="C6" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="58" t="s">
+      <c r="D6" s="64" t="s">
         <v>75</v>
       </c>
-      <c r="E6" s="58"/>
+      <c r="E6" s="64"/>
       <c r="F6" s="31"/>
       <c r="G6" s="31"/>
       <c r="H6" s="31"/>
       <c r="I6" s="31"/>
       <c r="J6" s="31"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B7" s="31"/>
       <c r="C7" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="59">
+      <c r="D7" s="63">
         <v>46098</v>
       </c>
-      <c r="E7" s="58"/>
+      <c r="E7" s="64"/>
       <c r="F7" s="31"/>
       <c r="G7" s="31"/>
       <c r="H7" s="31"/>
       <c r="I7" s="31"/>
       <c r="J7" s="31"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B8" s="31"/>
       <c r="C8" s="31"/>
       <c r="D8" s="31"/>
@@ -1991,7 +2020,7 @@
       <c r="I8" s="31"/>
       <c r="J8" s="31"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="36" t="s">
         <v>4</v>
       </c>
@@ -2010,7 +2039,7 @@
       <c r="I9" s="31"/>
       <c r="J9" s="31"/>
     </row>
-    <row r="10" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B10" s="37">
         <v>1</v>
       </c>
@@ -2029,7 +2058,7 @@
       <c r="I10" s="31"/>
       <c r="J10" s="31"/>
     </row>
-    <row r="11" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="B11" s="37">
         <f t="shared" ref="B11:B30" si="0">B10+1</f>
         <v>2</v>
@@ -2049,7 +2078,7 @@
       <c r="I11" s="31"/>
       <c r="J11" s="31"/>
     </row>
-    <row r="12" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B12" s="37">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2069,7 +2098,7 @@
       <c r="I12" s="31"/>
       <c r="J12" s="31"/>
     </row>
-    <row r="13" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B13" s="37">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2089,7 +2118,7 @@
       <c r="I13" s="31"/>
       <c r="J13" s="31"/>
     </row>
-    <row r="14" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B14" s="37">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2109,7 +2138,7 @@
       <c r="I14" s="31"/>
       <c r="J14" s="31"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B15" s="37">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2129,7 +2158,7 @@
       <c r="I15" s="31"/>
       <c r="J15" s="31"/>
     </row>
-    <row r="16" spans="1:10" ht="116" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
       <c r="B16" s="37">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2149,7 +2178,7 @@
       <c r="I16" s="31"/>
       <c r="J16" s="31"/>
     </row>
-    <row r="17" spans="2:10" ht="29" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B17" s="37">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2169,7 +2198,7 @@
       <c r="I17" s="31"/>
       <c r="J17" s="31"/>
     </row>
-    <row r="18" spans="2:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B18" s="37">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2189,7 +2218,7 @@
       <c r="I18" s="31"/>
       <c r="J18" s="31"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19" s="32">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2203,7 +2232,7 @@
       <c r="I19" s="31"/>
       <c r="J19" s="31"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" s="32">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2217,7 +2246,7 @@
       <c r="I20" s="31"/>
       <c r="J20" s="31"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" s="32">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2231,7 +2260,7 @@
       <c r="I21" s="31"/>
       <c r="J21" s="31"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B22" s="32">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2245,7 +2274,7 @@
       <c r="I22" s="31"/>
       <c r="J22" s="31"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B23" s="32">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2259,7 +2288,7 @@
       <c r="I23" s="31"/>
       <c r="J23" s="31"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B24" s="32">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -2273,7 +2302,7 @@
       <c r="I24" s="31"/>
       <c r="J24" s="31"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B25" s="32">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -2287,7 +2316,7 @@
       <c r="I25" s="31"/>
       <c r="J25" s="31"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B26" s="32">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2301,7 +2330,7 @@
       <c r="I26" s="31"/>
       <c r="J26" s="31"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B27" s="32">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -2315,7 +2344,7 @@
       <c r="I27" s="31"/>
       <c r="J27" s="31"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B28" s="32">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -2329,7 +2358,7 @@
       <c r="I28" s="31"/>
       <c r="J28" s="31"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B29" s="32">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -2343,7 +2372,7 @@
       <c r="I29" s="31"/>
       <c r="J29" s="31"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B30" s="32">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -2357,7 +2386,7 @@
       <c r="I30" s="31"/>
       <c r="J30" s="31"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B31" s="31"/>
       <c r="C31" s="31"/>
       <c r="D31" s="31"/>
@@ -2368,7 +2397,7 @@
       <c r="I31" s="31"/>
       <c r="J31" s="31"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B32" s="31"/>
       <c r="C32" s="42" t="s">
         <v>8</v>
@@ -2383,7 +2412,7 @@
       <c r="I32" s="31"/>
       <c r="J32" s="31"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B33" s="31"/>
       <c r="C33" s="31"/>
       <c r="D33" s="31"/>
@@ -2394,7 +2423,7 @@
       <c r="I33" s="31"/>
       <c r="J33" s="31"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="31"/>
       <c r="C34" s="31"/>
       <c r="D34" s="31"/>
@@ -2420,25 +2449,25 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:J35"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.90625" style="6"/>
-    <col min="2" max="2" width="12.1796875" style="6" customWidth="1"/>
-    <col min="3" max="3" width="16.1796875" style="6" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" style="6"/>
+    <col min="2" max="2" width="12.21875" style="6" customWidth="1"/>
+    <col min="3" max="3" width="16.21875" style="6" customWidth="1"/>
     <col min="4" max="4" width="18" style="6" customWidth="1"/>
-    <col min="5" max="5" width="23.90625" style="6" customWidth="1"/>
-    <col min="6" max="6" width="16.6328125" style="6" customWidth="1"/>
-    <col min="7" max="8" width="8.90625" style="6"/>
-    <col min="9" max="9" width="26.81640625" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="8.90625" style="6"/>
+    <col min="5" max="5" width="23.88671875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" style="6" customWidth="1"/>
+    <col min="7" max="8" width="8.88671875" style="6"/>
+    <col min="9" max="9" width="26.77734375" style="6" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="4"/>
       <c r="B1" s="30" t="s">
         <v>3</v>
@@ -2453,13 +2482,13 @@
       <c r="I1" s="55"/>
       <c r="J1" s="55"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B2" s="56" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B2" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
       <c r="F2" s="31"/>
       <c r="H2" s="3"/>
       <c r="I2" s="17" t="s">
@@ -2469,7 +2498,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B3" s="31"/>
       <c r="C3" s="31"/>
       <c r="D3" s="31"/>
@@ -2485,15 +2514,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B4" s="31"/>
       <c r="C4" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="57" t="s">
+      <c r="D4" s="66" t="s">
         <v>101</v>
       </c>
-      <c r="E4" s="57"/>
+      <c r="E4" s="66"/>
       <c r="F4" s="31"/>
       <c r="H4" s="16" t="s">
         <v>21</v>
@@ -2505,15 +2534,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B5" s="31"/>
       <c r="C5" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="58" t="s">
+      <c r="D5" s="64" t="s">
         <v>75</v>
       </c>
-      <c r="E5" s="58"/>
+      <c r="E5" s="64"/>
       <c r="F5" s="31"/>
       <c r="H5" s="16" t="s">
         <v>22</v>
@@ -2525,32 +2554,32 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" s="34"/>
       <c r="C6" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="59">
+      <c r="D6" s="63">
         <v>46098</v>
       </c>
-      <c r="E6" s="58"/>
+      <c r="E6" s="64"/>
       <c r="F6" s="31"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B7" s="31"/>
       <c r="C7" s="31"/>
       <c r="D7" s="31"/>
       <c r="E7" s="31"/>
       <c r="F7" s="31"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B8" s="31"/>
       <c r="C8" s="31"/>
       <c r="D8" s="31"/>
       <c r="E8" s="31"/>
       <c r="F8" s="31"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="36" t="s">
         <v>4</v>
       </c>
@@ -2567,7 +2596,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="B10" s="45">
         <v>1</v>
       </c>
@@ -2584,7 +2613,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B11" s="37">
         <f t="shared" ref="B11:B30" si="0">B10+1</f>
         <v>2</v>
@@ -2602,7 +2631,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" ht="39.6" x14ac:dyDescent="0.3">
       <c r="B12" s="37">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2620,7 +2649,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="62.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" ht="66" x14ac:dyDescent="0.3">
       <c r="B13" s="37">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2638,7 +2667,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="87" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="B14" s="37">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2656,7 +2685,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="87" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="B15" s="37">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2674,7 +2703,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B16" s="50">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2684,7 +2713,7 @@
       <c r="E16" s="52"/>
       <c r="F16" s="52"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" s="32">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2694,7 +2723,7 @@
       <c r="E17" s="41"/>
       <c r="F17" s="41"/>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="32">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2704,7 +2733,7 @@
       <c r="E18" s="41"/>
       <c r="F18" s="41"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="32">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2714,7 +2743,7 @@
       <c r="E19" s="41"/>
       <c r="F19" s="41"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B20" s="32">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2724,7 +2753,7 @@
       <c r="E20" s="41"/>
       <c r="F20" s="41"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B21" s="32">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2734,7 +2763,7 @@
       <c r="E21" s="41"/>
       <c r="F21" s="41"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B22" s="32">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2744,7 +2773,7 @@
       <c r="E22" s="41"/>
       <c r="F22" s="41"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B23" s="32">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2754,7 +2783,7 @@
       <c r="E23" s="41"/>
       <c r="F23" s="41"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B24" s="32">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -2764,7 +2793,7 @@
       <c r="E24" s="41"/>
       <c r="F24" s="41"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B25" s="32">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -2774,7 +2803,7 @@
       <c r="E25" s="41"/>
       <c r="F25" s="41"/>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B26" s="32">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2784,7 +2813,7 @@
       <c r="E26" s="41"/>
       <c r="F26" s="41"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B27" s="32">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -2794,7 +2823,7 @@
       <c r="E27" s="40"/>
       <c r="F27" s="40"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B28" s="32">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -2804,7 +2833,7 @@
       <c r="E28" s="41"/>
       <c r="F28" s="41"/>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B29" s="32">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -2814,7 +2843,7 @@
       <c r="E29" s="41"/>
       <c r="F29" s="41"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B30" s="32">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -2824,23 +2853,23 @@
       <c r="E30" s="41"/>
       <c r="F30" s="41"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B31" s="31"/>
       <c r="C31" s="31"/>
       <c r="D31" s="31"/>
       <c r="E31" s="31"/>
       <c r="F31" s="31"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B32" s="31"/>
-      <c r="C32" s="54" t="s">
+      <c r="C32" s="69" t="s">
         <v>126</v>
       </c>
-      <c r="D32" s="54"/>
-      <c r="E32" s="54"/>
+      <c r="D32" s="69"/>
+      <c r="E32" s="69"/>
       <c r="F32" s="53"/>
     </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F35" s="18"/>
     </row>
   </sheetData>
